--- a/docs/3.项目进度计划.xlsx
+++ b/docs/3.项目进度计划.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t>3.项目进度计划</t>
   </si>
@@ -85,14 +85,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="134"/>
-      </rPr>
-      <t>进度</t>
-    </r>
+    <t>进度</t>
   </si>
   <si>
     <r>
@@ -222,13 +215,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -885,8 +877,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -895,12 +890,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="58" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -916,16 +917,16 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1460,532 +1461,584 @@
     <col min="3" max="3" width="29.6814159292035" customWidth="1"/>
     <col min="4" max="4" width="13.212389380531" customWidth="1"/>
     <col min="5" max="5" width="13.8141592920354" customWidth="1"/>
-    <col min="7" max="7" width="9.83185840707965" customWidth="1"/>
+    <col min="7" max="7" width="9.83185840707965" style="1" customWidth="1"/>
     <col min="8" max="8" width="7.38053097345133" customWidth="1"/>
     <col min="9" max="9" width="14.6106194690265" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="31" customHeight="1" spans="1:20">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="8">
         <v>46248</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="8">
         <v>46249</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="8">
         <v>46251</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="8">
         <v>46252</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="8">
         <v>46253</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="8">
         <v>46254</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="8">
         <v>46255</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="8">
         <v>46257</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="8">
         <v>46258</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="8">
         <v>46259</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="8">
         <v>46260</v>
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" s="6">
+      <c r="A4" s="9">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="9">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="11">
         <v>46248</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>46251</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11" t="s">
+      <c r="G4" s="13">
+        <v>1</v>
+      </c>
+      <c r="H4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" ht="24.05" customHeight="1" spans="1:20">
-      <c r="A5" s="12">
+      <c r="A5" s="14">
         <v>1</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="11" t="s">
+      <c r="D5" s="11">
+        <v>46248</v>
+      </c>
+      <c r="E5" s="11">
+        <v>46248</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13">
+        <v>1</v>
+      </c>
+      <c r="H5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="9"/>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" ht="24.05" customHeight="1" spans="1:20">
-      <c r="A6" s="12">
+      <c r="A6" s="14">
         <v>1.1</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="11">
+      <c r="D6" s="11">
+        <v>46248</v>
+      </c>
+      <c r="E6" s="11">
+        <v>46248</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13">
+        <v>1</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" ht="24.05" customHeight="1" spans="1:20">
+      <c r="A7" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="11">
+        <v>46248</v>
+      </c>
+      <c r="E7" s="11">
+        <v>46251</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13">
+        <v>1</v>
+      </c>
+      <c r="H7" s="14">
         <v>1.1</v>
       </c>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" ht="24.05" customHeight="1" spans="1:20">
-      <c r="A7" s="12">
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="9">
+        <v>2</v>
+      </c>
+      <c r="B8" s="9">
+        <v>2</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="11">
+        <v>46251</v>
+      </c>
+      <c r="E8" s="11">
+        <v>46253</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="H8" s="9">
+        <v>1</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" ht="24.05" customHeight="1" spans="1:20">
+      <c r="A9" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="11">
+        <v>46251</v>
+      </c>
+      <c r="E9" s="11">
+        <v>46251</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14">
         <v>1.2</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="11">
-        <v>1.2</v>
-      </c>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" spans="1:20">
-      <c r="A8" s="6">
+      <c r="I9" s="12"/>
+    </row>
+    <row r="10" ht="24.05" customHeight="1" spans="1:20">
+      <c r="A10" s="14">
+        <v>2.2</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="11">
+        <v>46251</v>
+      </c>
+      <c r="E10" s="11">
+        <v>46252</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="H10" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" ht="24.05" customHeight="1" spans="1:20">
+      <c r="A11" s="14">
+        <v>2.3</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="11">
+        <v>46252</v>
+      </c>
+      <c r="E11" s="11">
+        <v>46252</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="16">
+        <v>1</v>
+      </c>
+      <c r="H11" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" ht="24.05" customHeight="1" spans="1:20">
+      <c r="A12" s="14">
+        <v>2.4</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="11">
+        <v>46252</v>
+      </c>
+      <c r="E12" s="11">
+        <v>46252</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="16">
+        <v>1</v>
+      </c>
+      <c r="H12" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" ht="24.05" customHeight="1" spans="1:20">
+      <c r="A13" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="11">
+        <v>46252</v>
+      </c>
+      <c r="E13" s="11">
+        <v>46252</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="16">
+        <v>1</v>
+      </c>
+      <c r="H13" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" ht="24.05" customHeight="1" spans="1:20">
+      <c r="A14" s="14">
+        <v>2.6</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="9">
+        <v>3</v>
+      </c>
+      <c r="B15" s="9">
+        <v>3</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="11">
+        <v>46254</v>
+      </c>
+      <c r="E15" s="11">
+        <v>46260</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="9">
         <v>2</v>
       </c>
-      <c r="B8" s="6">
-        <v>2</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="8">
-        <v>46251</v>
-      </c>
-      <c r="E8" s="8">
-        <v>46253</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="6">
-        <v>1</v>
-      </c>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" ht="24.05" customHeight="1" spans="1:20">
-      <c r="A9" s="12">
-        <v>2.1</v>
-      </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="11">
-        <v>1.3</v>
-      </c>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" ht="24.05" customHeight="1" spans="1:20">
-      <c r="A10" s="12">
-        <v>2.2</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="11">
-        <v>2.1</v>
-      </c>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" ht="24.05" customHeight="1" spans="1:20">
-      <c r="A11" s="12">
-        <v>2.3</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11">
-        <v>2.1</v>
-      </c>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" ht="24.05" customHeight="1" spans="1:20">
-      <c r="A12" s="12">
-        <v>2.4</v>
-      </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="11">
-        <v>2.1</v>
-      </c>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" ht="24.05" customHeight="1" spans="1:20">
-      <c r="A13" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="11">
-        <v>2.1</v>
-      </c>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" ht="24.05" customHeight="1" spans="1:20">
-      <c r="A14" s="12">
-        <v>2.6</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" spans="1:20">
-      <c r="A15" s="6">
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" ht="24.05" customHeight="1" spans="1:20">
+      <c r="A16" s="14">
+        <v>3.1</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="12"/>
+    </row>
+    <row r="17" ht="24.05" customHeight="1" spans="1:9">
+      <c r="A17" s="14">
+        <v>3.2</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="14">
+        <v>3.1</v>
+      </c>
+      <c r="I17" s="12"/>
+    </row>
+    <row r="18" ht="24.05" customHeight="1" spans="1:9">
+      <c r="A18" s="14">
+        <v>3.3</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="14">
+        <v>3.2</v>
+      </c>
+      <c r="I18" s="12"/>
+    </row>
+    <row r="19" ht="24.05" customHeight="1" spans="1:9">
+      <c r="A19" s="14">
+        <v>3.4</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="14">
+        <v>3.3</v>
+      </c>
+      <c r="I19" s="12"/>
+    </row>
+    <row r="20" ht="24.05" customHeight="1" spans="1:9">
+      <c r="A20" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="14">
+        <v>3.3</v>
+      </c>
+      <c r="I20" s="12"/>
+    </row>
+    <row r="21" ht="24.05" customHeight="1" spans="1:9">
+      <c r="A21" s="14">
+        <v>3.6</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="I21" s="12"/>
+    </row>
+    <row r="22" ht="24.05" customHeight="1" spans="1:9">
+      <c r="A22" s="14">
+        <v>3.7</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="14">
+        <v>3.6</v>
+      </c>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="9">
+        <v>4</v>
+      </c>
+      <c r="B23" s="9">
+        <v>4</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="11">
+        <v>46260</v>
+      </c>
+      <c r="E23" s="11">
+        <v>46260</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="9">
         <v>3</v>
       </c>
-      <c r="B15" s="6">
-        <v>3</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="8">
-        <v>46254</v>
-      </c>
-      <c r="E15" s="8">
-        <v>46260</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="6">
-        <v>2</v>
-      </c>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" ht="24.05" customHeight="1" spans="1:20">
-      <c r="A16" s="12">
-        <v>3.1</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="11" t="s">
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" ht="24.05" customHeight="1" spans="1:9">
+      <c r="A24" s="14">
+        <v>4.1</v>
+      </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" ht="24.05" customHeight="1" spans="1:9">
-      <c r="A17" s="12">
-        <v>3.2</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11">
-        <v>3.1</v>
-      </c>
-      <c r="I17" s="9"/>
-    </row>
-    <row r="18" ht="24.05" customHeight="1" spans="1:9">
-      <c r="A18" s="12">
-        <v>3.3</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="11">
-        <v>3.2</v>
-      </c>
-      <c r="I18" s="9"/>
-    </row>
-    <row r="19" ht="24.05" customHeight="1" spans="1:9">
-      <c r="A19" s="12">
-        <v>3.4</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="11">
-        <v>3.3</v>
-      </c>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" ht="24.05" customHeight="1" spans="1:9">
-      <c r="A20" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="11">
-        <v>3.3</v>
-      </c>
-      <c r="I20" s="9"/>
-    </row>
-    <row r="21" ht="24.05" customHeight="1" spans="1:9">
-      <c r="A21" s="12">
-        <v>3.6</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I21" s="9"/>
-    </row>
-    <row r="22" ht="24.05" customHeight="1" spans="1:9">
-      <c r="A22" s="12">
-        <v>3.7</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="11">
-        <v>3.6</v>
-      </c>
-      <c r="I22" s="9"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="6">
-        <v>4</v>
-      </c>
-      <c r="B23" s="6">
-        <v>4</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="8">
-        <v>46260</v>
-      </c>
-      <c r="E23" s="8">
-        <v>46260</v>
-      </c>
-      <c r="F23" s="9" t="s">
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="9">
+        <v>5</v>
+      </c>
+      <c r="B25" s="9">
+        <v>5</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="11">
+        <v>46261</v>
+      </c>
+      <c r="E25" s="11">
+        <v>46261</v>
+      </c>
+      <c r="F25" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="6">
-        <v>3</v>
-      </c>
-      <c r="I23" s="9"/>
-    </row>
-    <row r="24" ht="24.05" customHeight="1" spans="1:9">
-      <c r="A24" s="12">
-        <v>4.1</v>
-      </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="11" t="s">
+      <c r="G25" s="13"/>
+      <c r="H25" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I24" s="9"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="6">
-        <v>5</v>
-      </c>
-      <c r="B25" s="6">
-        <v>5</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" s="8">
-        <v>46261</v>
-      </c>
-      <c r="E25" s="8">
-        <v>46261</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I25" s="9"/>
+      <c r="I25" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="21">
